--- a/resultados/ubirata/erros_varredura.xlsx
+++ b/resultados/ubirata/erros_varredura.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/mapa-do-site/ubirata.oxy.elotech.com.br/cidadao/</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/publicacoes/28/8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-04 00:17:03</t>
+          <t>2026-08-04 19:02:37</t>
         </is>
       </c>
     </row>
@@ -484,23 +484,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/mapa-do-site/ubirata.oxy.elotech.com.br/cidadao/</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/diario-oficial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-04 00:17:15</t>
+          <t>2026-08-04 19:03:09</t>
         </is>
       </c>
     </row>
@@ -512,23 +512,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/ubirata-fecha-primeiro-semestre-com-superavit-de-mais-de-r-2-milhoes/www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/licitacoes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-04 00:20:42</t>
+          <t>2026-08-04 19:03:21</t>
         </is>
       </c>
     </row>
@@ -540,23 +540,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/ubirata-fecha-primeiro-semestre-com-superavit-de-mais-de-r-2-milhoes/www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/licitacoes-agendamentos-calendario</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-04 00:21:12</t>
+          <t>2026-08-04 19:03:32</t>
         </is>
       </c>
     </row>
@@ -568,23 +568,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/prefeitura-abre-concurso-para-agente-de-saude/www.exatuspr.com.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/publicacoes/41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-04 00:24:36</t>
+          <t>2026-08-04 19:03:44</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/prefeitura-abre-concurso-para-agente-de-saude/www.exatuspr.com.br/</t>
+          <t>https://www.ubirata.pr.gov.br/mapa-do-site/ubirata.oxy.elotech.com.br/cidadao/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,11 +608,2195 @@
         <v>404</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:03:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/mapa-do-site/ubirata.oxy.elotech.com.br/cidadao/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>404</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/authenticate?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0&amp;execution=ca7f3351-2c0b-4160-923e-917d9d473ffa&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>400</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:05:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/broker/google/login?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0&amp;session_code=u1FyoiTb5b08DFopHgm7k1XXbJbng4qawLHsONKd7Q8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>400</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:05:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/registration?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>400</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/reset-credentials?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>400</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/authenticate?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ&amp;execution=ca7f3351-2c0b-4160-923e-917d9d473ffa&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/registration?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>400</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/reset-credentials?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>400</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:06:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/broker/google/login?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ&amp;session_code=tJQ94jZ98uoIiKwEtJhWwGLVZw9YBY7FfSn1nwFLyt4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>400</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:06:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>400</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:22:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:22:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>400</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0&amp;session_code=jKnhV77gwPxER_ERC3hJRrzzqvAkfGQQaUHbJlyqZro</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>400</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>400</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>400</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ&amp;session_code=n4O22tAcyqbXagSP_wF-QOyRmMoDF1CA58To25hFRHs</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>400</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>400</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:23:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>400</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0&amp;session_code=D662ea6N04QnptbaLB5ur0gfGe1iAlervMmc9EeUQyk</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>400</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:24:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>400</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:24:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>400</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:24:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>400</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:24:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9&amp;session_code=fC5gV88_pwbyxoGv9H9j-CyG7MD9iEU-QX1mewah6RE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>400</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:24:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/publicacoes/117</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:30:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/ubirata-fecha-primeiro-semestre-com-superavit-de-mais-de-r-2-milhoes/www.ubirata.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>404</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:12:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/ubirata-fecha-primeiro-semestre-com-superavit-de-mais-de-r-2-milhoes/www.ubirata.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>404</v>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:12:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/prefeitura-abre-concurso-para-agente-de-saude/www.exatuspr.com.br/</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>404</v>
+      </c>
+      <c r="E36" t="n">
         <v>8</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-04 00:24:49</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:15:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/prefeitura-abre-concurso-para-agente-de-saude/www.exatuspr.com.br/</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>404</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:15:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/authenticate?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0&amp;execution=ca7f3351-2c0b-4160-923e-917d9d473ffa&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>400</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:18:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/authenticate?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0&amp;execution=ca7f3351-2c0b-4160-923e-917d9d473ffa&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>400</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/broker/google/login?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0&amp;session_code=u1FyoiTb5b08DFopHgm7k1XXbJbng4qawLHsONKd7Q8</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>400</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/broker/google/login?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0&amp;session_code=u1FyoiTb5b08DFopHgm7k1XXbJbng4qawLHsONKd7Q8</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>400</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:18:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/registration?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>400</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:18:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/registration?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>400</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/reset-credentials?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>400</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/reset-credentials?client_id=portal-govdigital-frontend&amp;tab_id=UrGxoBy3Xm0&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvZ292ZXJuby1kaWdpdGFsL3NlcnZpZG9yIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNzFmYzQ4NDUtMjhhZS00ZDkyLTk0NDctOWExODJjYzU1YjI4In0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>400</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/authenticate?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ&amp;execution=ca7f3351-2c0b-4160-923e-917d9d473ffa&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>400</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/authenticate?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ&amp;execution=ca7f3351-2c0b-4160-923e-917d9d473ffa&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>400</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/registration?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>400</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/registration?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>400</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/reset-credentials?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>400</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/login-actions/reset-credentials?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>400</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/broker/google/login?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ&amp;session_code=tJQ94jZ98uoIiKwEtJhWwGLVZw9YBY7FfSn1nwFLyt4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>400</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata-externo/broker/google/login?client_id=itbi-cidadao&amp;tab_id=g5veF65yHWM&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY2lkYWRhby8iLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI2YWI2MGE2ZC1jODViLTQzMTMtYmZlMy0zZmY2N2FmNGE3YjEifQ&amp;session_code=tJQ94jZ98uoIiKwEtJhWwGLVZw9YBY7FfSn1nwFLyt4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>400</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>400</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>400</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>400</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:19:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>400</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:20:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>400</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>400</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:20:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0&amp;session_code=jKnhV77gwPxER_ERC3hJRrzzqvAkfGQQaUHbJlyqZro</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>400</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=0coc0gqTgfE&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvY29udHJpYnVpbnRlIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiZjY4NzEwYzQtM2ZjNS00NmY3LTgyOTMtNDFkY2RlZDhmMTcxIn0&amp;session_code=jKnhV77gwPxER_ERC3hJRrzzqvAkfGQQaUHbJlyqZro</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>400</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>400</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>400</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>400</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>400</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>400</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>400</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ&amp;session_code=n4O22tAcyqbXagSP_wF-QOyRmMoDF1CA58To25hFRHs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>400</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=HpmRYCf7hyU&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc2Vydmlkb3IiLCJydCI6ImNvZGUiLCJybSI6ImZyYWdtZW50Iiwic3QiOiI4ZDdmMTJlNy1mZTA1LTQ3MjctODJiNy02ZDBjYzViMWFhOWIifQ&amp;session_code=n4O22tAcyqbXagSP_wF-QOyRmMoDF1CA58To25hFRHs</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>400</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>400</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>400</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>400</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>400</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>400</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>400</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0&amp;session_code=D662ea6N04QnptbaLB5ur0gfGe1iAlervMmc9EeUQyk</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>400</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=Uo_mzwvCnas&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzIiwicnQiOiJjb2RlIiwicm0iOiJmcmFnbWVudCIsInN0IjoiNTRhZTk0YjMtMDhjYy00ODJhLTk4NzctNzZmZDUyODMzMDk4In0&amp;session_code=D662ea6N04QnptbaLB5ur0gfGe1iAlervMmc9EeUQyk</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>400</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>400</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/authenticate?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9&amp;execution=78460044-1ffa-44e4-beb4-f61cfdb21db6&amp;kc_locale=pt-BR</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>400</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>400</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/registration?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>400</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>400</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/login-actions/reset-credentials?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>400</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9&amp;session_code=fC5gV88_pwbyxoGv9H9j-CyG7MD9iEU-QX1mewah6RE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>400</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://ubirata.oxy.elotech.com.br/auth/realms/ubirata/broker/google/login?client_id=minha-conta-frontend&amp;tab_id=2NkK3UVQ17o&amp;client_data=eyJydSI6Imh0dHBzOi8vdWJpcmF0YS5veHkuZWxvdGVjaC5jb20uYnIvc29saWNpdGFjb2VzL2NvbnN1bHRhciIsInJ0IjoiY29kZSIsInJtIjoiZnJhZ21lbnQiLCJzdCI6IjIyZTZjZmM5LTQ1YmEtNGUzMS1hNzJhLTA1NTE3YTM4NTZiYiJ9&amp;session_code=fC5gV88_pwbyxoGv9H9j-CyG7MD9iEU-QX1mewah6RE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HTTP_400</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>400</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:22:34</t>
         </is>
       </c>
     </row>
